--- a/public/upload/report/REKAP KEUANGAN YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 10 TAHUN 2026.xlsx
+++ b/public/upload/report/REKAP KEUANGAN YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 10 TAHUN 2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
   <si>
     <t>LAPORAN KEUANGAN YAYASAN PENDIDIKAN ALQALAM KENDARI</t>
   </si>
@@ -65,16 +65,19 @@
     <t>Bayar listrik yayasan</t>
   </si>
   <si>
+    <t>Terima pengembalian pinjaman ustadzah Evalina (lunas)</t>
+  </si>
+  <si>
+    <t>Pengembalian pinjaman atas bu Nurlina</t>
+  </si>
+  <si>
+    <t>Pengembalian pinjaman a.n Ustadz Adi</t>
+  </si>
+  <si>
+    <t>Kamis/ 15 Oktober 2026</t>
+  </si>
+  <si>
     <t>Penarikan dari BMT Assalam</t>
-  </si>
-  <si>
-    <t>Terima pengembalian pinjaman ustadzah Evalina (lunas)</t>
-  </si>
-  <si>
-    <t>Pengembalian pinjaman atas bu Nurlina</t>
-  </si>
-  <si>
-    <t>Pengembalian pinjaman a.n Ustadz Adi</t>
   </si>
 </sst>
 </file>
@@ -573,7 +576,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4">
-        <v>301</v>
+        <v>99</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
@@ -585,12 +588,12 @@
         <v>16</v>
       </c>
       <c r="F8" s="6">
-        <v>10468000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6">
         <f>H7+F8-G8</f>
-        <v>28058214</v>
+        <v>18090214</v>
       </c>
       <c r="I8" s="3"/>
     </row>
@@ -598,9 +601,7 @@
       <c r="A9" s="4">
         <v>4</v>
       </c>
-      <c r="B9" s="4">
-        <v>99</v>
-      </c>
+      <c r="B9" s="4"/>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
@@ -616,7 +617,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6">
         <f>H8+F9-G9</f>
-        <v>28558214</v>
+        <v>18590214</v>
       </c>
       <c r="I9" s="3"/>
     </row>
@@ -635,12 +636,12 @@
         <v>18</v>
       </c>
       <c r="F10" s="6">
-        <v>500000.0</v>
+        <v>200000.0</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6">
         <f>H9+F10-G10</f>
-        <v>29058214</v>
+        <v>18790214</v>
       </c>
       <c r="I10" s="3"/>
     </row>
@@ -648,18 +649,20 @@
       <c r="A11" s="4">
         <v>6</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="4">
+        <v>301</v>
+      </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="6">
-        <v>200000.0</v>
+        <v>10468000.0</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6">

--- a/public/upload/report/REKAP KEUANGAN YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 10 TAHUN 2026.xlsx
+++ b/public/upload/report/REKAP KEUANGAN YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 10 TAHUN 2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
   <si>
     <t>LAPORAN KEUANGAN YAYASAN PENDIDIKAN ALQALAM KENDARI</t>
   </si>
@@ -23,61 +23,160 @@
     <t>BULAN 10 TAHUN 2026</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Kode</t>
-  </si>
-  <si>
-    <t>Hari/Tanggal</t>
-  </si>
-  <si>
-    <t>Nama</t>
+    <t>SALDO</t>
+  </si>
+  <si>
+    <t>PEMASUKAN</t>
+  </si>
+  <si>
+    <t>No.</t>
   </si>
   <si>
     <t>Uraian</t>
   </si>
   <si>
-    <t>Debet</t>
-  </si>
-  <si>
-    <t>Kredit</t>
-  </si>
-  <si>
-    <t>Saldo</t>
-  </si>
-  <si>
-    <t>Keterangan</t>
-  </si>
-  <si>
-    <t>Rabu/ 30 September 2026</t>
-  </si>
-  <si>
-    <t>Saldo bulan sebelumnya</t>
-  </si>
-  <si>
-    <t>Kamis/ 08 Oktober 2026</t>
-  </si>
-  <si>
-    <t>bendahara_yayasan</t>
-  </si>
-  <si>
-    <t>Bayar listrik yayasan</t>
-  </si>
-  <si>
-    <t>Terima pengembalian pinjaman ustadzah Evalina (lunas)</t>
-  </si>
-  <si>
-    <t>Pengembalian pinjaman atas bu Nurlina</t>
-  </si>
-  <si>
-    <t>Pengembalian pinjaman a.n Ustadz Adi</t>
-  </si>
-  <si>
-    <t>Kamis/ 15 Oktober 2026</t>
-  </si>
-  <si>
-    <t>Penarikan dari BMT Assalam</t>
+    <t>Penarikan Assalam</t>
+  </si>
+  <si>
+    <t>Penarikan Bank Muamalat</t>
+  </si>
+  <si>
+    <t>Pengembalian dana kegiatan</t>
+  </si>
+  <si>
+    <t>Pengembalian pinjaman pegawai / unit</t>
+  </si>
+  <si>
+    <t>Raport TK</t>
+  </si>
+  <si>
+    <t>Pendapatan Lainnya</t>
+  </si>
+  <si>
+    <t>Administrasi penelitian</t>
+  </si>
+  <si>
+    <t>TOTAL 1-7</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PENGELUARAN</t>
+  </si>
+  <si>
+    <t>Catering YAS</t>
+  </si>
+  <si>
+    <t>Snack siswa dan guru YAS</t>
+  </si>
+  <si>
+    <t>Belanja kantor &amp; ATK</t>
+  </si>
+  <si>
+    <t>Gaji OB SDIT, SMPIT</t>
+  </si>
+  <si>
+    <t>BPJS</t>
+  </si>
+  <si>
+    <t>Penggajian TKIT, MBC, dan SMPIT</t>
+  </si>
+  <si>
+    <t>Pembimbingan olimpiade / beasiswa</t>
+  </si>
+  <si>
+    <t>Wifi</t>
+  </si>
+  <si>
+    <t>Gaji Guru SDIT</t>
+  </si>
+  <si>
+    <t>Pembayaran koran</t>
+  </si>
+  <si>
+    <t>THR</t>
+  </si>
+  <si>
+    <t>RAB Unit</t>
+  </si>
+  <si>
+    <t>Administrasi transfer / sekretariatan</t>
+  </si>
+  <si>
+    <t>Penggajian YAS, USQ, SMAIT</t>
+  </si>
+  <si>
+    <t>Kampung Inggris</t>
+  </si>
+  <si>
+    <t>Mesjid Al Qalam</t>
+  </si>
+  <si>
+    <t>Setoran ke rekening BMT</t>
+  </si>
+  <si>
+    <t>Pinjaman pegawai / unit</t>
+  </si>
+  <si>
+    <t>Listrik dan kelistrikan Al Qalam</t>
+  </si>
+  <si>
+    <t>Pengembalian dana PPDB / SPP / Catering ke ortu siswa</t>
+  </si>
+  <si>
+    <t>Operasional / grab / transport</t>
+  </si>
+  <si>
+    <t>Iuran JSIT</t>
+  </si>
+  <si>
+    <t>Snack Rapat / Tamu</t>
+  </si>
+  <si>
+    <t>Kursi SMP dan SD</t>
+  </si>
+  <si>
+    <t>Galon</t>
+  </si>
+  <si>
+    <t>Program Al Qalam Peduli</t>
+  </si>
+  <si>
+    <t>Seragam Ummi Erni</t>
+  </si>
+  <si>
+    <t>Seragam guru SDIT</t>
+  </si>
+  <si>
+    <t>Pekerjaan Lugis RKB SDIT</t>
+  </si>
+  <si>
+    <t>Infaq sosial / bantuan pernikahan / Beasiswa</t>
+  </si>
+  <si>
+    <t>Kafalah marbot</t>
+  </si>
+  <si>
+    <t>Honor pegawai dapur</t>
+  </si>
+  <si>
+    <t>Pelatihan guru / studi banding / outbond</t>
+  </si>
+  <si>
+    <t>Dana pemateri</t>
+  </si>
+  <si>
+    <t>Tunjangan Pangan</t>
+  </si>
+  <si>
+    <t>Asrama Santri (kafalah, air, uang makan, sewa BTN)</t>
+  </si>
+  <si>
+    <t>Sarpras</t>
+  </si>
+  <si>
+    <t>Total 1-37</t>
   </si>
 </sst>
 </file>
@@ -140,26 +239,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,222 +545,496 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
-    <col min="2" max="2" width="8" customWidth="true" style="0"/>
-    <col min="3" max="3" width="30" customWidth="true" style="0"/>
-    <col min="4" max="4" width="20" customWidth="true" style="0"/>
-    <col min="5" max="5" width="70" customWidth="true" style="0"/>
-    <col min="6" max="6" width="17" customWidth="true" style="0"/>
-    <col min="7" max="7" width="17" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17" customWidth="true" style="0"/>
-    <col min="9" max="9" width="17" customWidth="true" style="0"/>
+    <col min="2" max="2" width="45" customWidth="true" style="0"/>
+    <col min="3" max="3" width="15" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="5" spans="1:9">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="3">
+        <v>17977204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="4">
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3" t="s">
+      <c r="B18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3">
+        <v>5</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3">
+        <v>6</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3">
+        <v>7</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3">
+        <v>9</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3">
+        <v>10</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3">
         <v>11</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
+      <c r="B28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3">
         <v>12</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6">
-        <v>17877204.0</v>
-      </c>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="4">
+      <c r="B29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3">
+        <v>14</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3">
+        <v>15</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3">
+        <v>16</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3">
+        <v>17</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3">
+        <v>18</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="3">
+        <v>19</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="3">
+        <v>20</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="3">
+        <v>21</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="3">
+        <v>22</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="3">
+        <v>23</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="3">
+        <v>24</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="3">
+        <v>25</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="3">
+        <v>26</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="3">
+        <v>27</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="3">
+        <v>28</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="3">
+        <v>29</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="3">
+        <v>30</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="3">
+        <v>31</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="3">
+        <v>32</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="3">
+        <v>33</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="3">
+        <v>34</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="3">
+        <v>35</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="3">
+        <v>36</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="3">
+        <v>37</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6">
-        <v>286990.0</v>
-      </c>
-      <c r="H7" s="6">
-        <f>H6+F7-G7</f>
-        <v>17590214</v>
-      </c>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="4">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4">
-        <v>99</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="6">
-        <v>500000.0</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6">
-        <f>H7+F8-G8</f>
-        <v>18090214</v>
-      </c>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="4">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="6">
-        <v>500000.0</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6">
-        <f>H8+F9-G9</f>
-        <v>18590214</v>
-      </c>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="4">
-        <v>5</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="6">
-        <v>200000.0</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
-        <f>H9+F10-G10</f>
-        <v>18790214</v>
-      </c>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="4">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4">
-        <v>301</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="6">
-        <v>10468000.0</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <f>H10+F11-G11</f>
-        <v>29258214</v>
-      </c>
-      <c r="I11" s="3"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
